--- a/output/pdf_financials_xlsx/SL.xlsx
+++ b/output/pdf_financials_xlsx/SL.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.012</v>
+        <v>0.079972</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.063612</v>
+        <v>0.165304</v>
       </c>
     </row>
     <row r="11">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.081024</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.013649</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.081024</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.013649</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.081024</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.107185</v>
+        <v>0.09353599999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">

--- a/output/pdf_financials_xlsx/SL.xlsx
+++ b/output/pdf_financials_xlsx/SL.xlsx
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.000826</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.001872</v>
       </c>
     </row>
     <row r="111">
@@ -2838,7 +2838,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.000826</v>
       </c>
